--- a/sources/jun_step5b.xlsx
+++ b/sources/jun_step5b.xlsx
@@ -774,6 +774,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>c3fb2b44-9abc-4fc9-8f10-b2e01504275a</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>c3fb2b44-9abc-4fc9-8f10-b2e01504275a</t>
@@ -821,6 +826,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4e122e09-243f-49b9-96ea-c109b7d9a02f</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>4e122e09-243f-49b9-96ea-c109b7d9a02f</t>
@@ -866,6 +876,11 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>30e2beaa-6d7c-42d2-8397-096837f7826d</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -6227,6 +6242,11 @@
           <t>mhmmmlmlmm</t>
         </is>
       </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>fcd205b6-5f94-4cfd-a61b-4cc522dbe599</t>
+        </is>
+      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>fcd205b6-5f94-4cfd-a61b-4cc522dbe599</t>
@@ -6259,6 +6279,11 @@
           <t>mhmmmlhhlh</t>
         </is>
       </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>91ec0924-2220-448a-88fb-9b64f00b6f0c</t>
+        </is>
+      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>91ec0924-2220-448a-88fb-9b64f00b6f0c</t>
@@ -6289,6 +6314,11 @@
       <c r="K110" t="inlineStr">
         <is>
           <t>mhmm</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>77355c32-3a7d-4d9f-8a8d-7ff03658cb77</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">

--- a/sources/jun_step5b.xlsx
+++ b/sources/jun_step5b.xlsx
@@ -4024,6 +4024,11 @@
           <t>– ~d</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>~db</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
           <t>– Strike Cancel</t>
@@ -4994,6 +4999,11 @@
       <c r="A84" t="inlineStr">
         <is>
           <t>– d</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>b</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
